--- a/Descarga Muestras/Registro.xlsx
+++ b/Descarga Muestras/Registro.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4605,8 +4605,448 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>[27-10-2025 12:03]</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2109081</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2100626</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2100627</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2100628</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2100629</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>[27-10-2025 12:08]</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2100626</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>212</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2100630</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>213</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2101463</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>214</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2100627</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>214</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2105958</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>215</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2100628</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>215</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2106100</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>216</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2100629</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>217</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>[27-10-2025 12:16]</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>218</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2106521</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>219</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2081247</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>220</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>[27-10-2025 15:54]</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>221</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2097180</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>222</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2094425</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E206"/>
+  <autoFilter ref="A1:E227"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Registro.xlsx
+++ b/Descarga Muestras/Registro.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5045,8 +5045,603 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>223</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>[19-01-2026 18:06]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>224</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>[19-01-2026 18:11]</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>225</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>[19-01-2026 18:15]</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>226</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2219923</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>227</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2252203</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>228</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2088388</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>229</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2174130</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>230</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2196789</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>231</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2216529</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>232</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2216575</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>233</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2258326</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>234</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2172478</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>235</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2262974</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>236</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2221229</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>237</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2270806</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>238</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2270917</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>239</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2281783</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>240</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2282349</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>241</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2229048</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>242</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2175973</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>243</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2022098</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>244</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2278126</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>245</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2232674</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>246</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2232675</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>247</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2232676</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>248</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2284161</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>249</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2284162</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>250</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2284209</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>251</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2199896</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E227"/>
+  <autoFilter ref="A1:E256"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Registro.xlsx
+++ b/Descarga Muestras/Registro.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$256</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$262</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5640,8 +5640,158 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>252</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>[21-01-2026 16:33]</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>253</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>[21-01-2026 17:48]</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>254</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>[21-01-2026 17:54]</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>255</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>[21-01-2026 18:02]</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>256</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>[21-01-2026 18:06]</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>257</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>[21-01-2026 18:15]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E256"/>
+  <autoFilter ref="A1:E262"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Registro.xlsx
+++ b/Descarga Muestras/Registro.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,8 +515,953 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[02-02-2026 12:59]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2196717</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2288013</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2288015</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2288016</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2295404</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2288011</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2288019</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2288017</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2281951</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2028740</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2261660</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2261661</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2266029</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2266077</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2266519</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2301547</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2298247</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2286184</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2288007</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2288018</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2283180</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2283182</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2271946</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2275110</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2275111</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2275118</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2270582</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2211963</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2211976</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2211978</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2212307</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2212342</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2212373</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1598805</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1598832</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1711706</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2074274</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2288020</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2288012</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2289063</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2238197</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2293048</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2293049</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2303935</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2301166</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2291532</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E50"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Descarga Muestras/Registro.xlsx
+++ b/Descarga Muestras/Registro.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$5149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$5445</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5149"/>
+  <dimension ref="A1:E5445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103907,8 +103907,5455 @@
         </is>
       </c>
     </row>
+    <row r="5150">
+      <c r="A5150" t="n">
+        <v>5149</v>
+      </c>
+      <c r="B5150" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5150" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5150" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5150" t="inlineStr">
+        <is>
+          <t>[09-02-2026 12:46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5151">
+      <c r="A5151" t="n">
+        <v>5150</v>
+      </c>
+      <c r="B5151" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5151" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5151" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5151" t="inlineStr">
+        <is>
+          <t>[09-02-2026 12:54]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5152">
+      <c r="A5152" t="n">
+        <v>5151</v>
+      </c>
+      <c r="B5152" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5153">
+      <c r="A5153" t="n">
+        <v>5152</v>
+      </c>
+      <c r="B5153" t="n">
+        <v>1609052</v>
+      </c>
+      <c r="C5153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5153" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5154">
+      <c r="A5154" t="n">
+        <v>5153</v>
+      </c>
+      <c r="B5154" t="n">
+        <v>1660635</v>
+      </c>
+      <c r="C5154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5154" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5155">
+      <c r="A5155" t="n">
+        <v>5154</v>
+      </c>
+      <c r="B5155" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5155" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5156">
+      <c r="A5156" t="n">
+        <v>5155</v>
+      </c>
+      <c r="B5156" t="n">
+        <v>1863061</v>
+      </c>
+      <c r="C5156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5157">
+      <c r="A5157" t="n">
+        <v>5156</v>
+      </c>
+      <c r="B5157" t="n">
+        <v>1916121</v>
+      </c>
+      <c r="C5157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5158">
+      <c r="A5158" t="n">
+        <v>5157</v>
+      </c>
+      <c r="B5158" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5159">
+      <c r="A5159" t="n">
+        <v>5158</v>
+      </c>
+      <c r="B5159" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5159" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5159" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5159" t="inlineStr">
+        <is>
+          <t>[09-02-2026 13:02]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5160">
+      <c r="A5160" t="n">
+        <v>5159</v>
+      </c>
+      <c r="B5160" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5161">
+      <c r="A5161" t="n">
+        <v>5160</v>
+      </c>
+      <c r="B5161" t="n">
+        <v>1609052</v>
+      </c>
+      <c r="C5161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5162">
+      <c r="A5162" t="n">
+        <v>5161</v>
+      </c>
+      <c r="B5162" t="n">
+        <v>1660635</v>
+      </c>
+      <c r="C5162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5163">
+      <c r="A5163" t="n">
+        <v>5162</v>
+      </c>
+      <c r="B5163" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5164">
+      <c r="A5164" t="n">
+        <v>5163</v>
+      </c>
+      <c r="B5164" t="n">
+        <v>1863061</v>
+      </c>
+      <c r="C5164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5164" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5165">
+      <c r="A5165" t="n">
+        <v>5164</v>
+      </c>
+      <c r="B5165" t="n">
+        <v>1916121</v>
+      </c>
+      <c r="C5165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5165" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5166">
+      <c r="A5166" t="n">
+        <v>5165</v>
+      </c>
+      <c r="B5166" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5166" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5167">
+      <c r="A5167" t="n">
+        <v>5166</v>
+      </c>
+      <c r="B5167" t="n">
+        <v>1936999</v>
+      </c>
+      <c r="C5167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5168">
+      <c r="A5168" t="n">
+        <v>5167</v>
+      </c>
+      <c r="B5168" t="n">
+        <v>1967077</v>
+      </c>
+      <c r="C5168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5169">
+      <c r="A5169" t="n">
+        <v>5168</v>
+      </c>
+      <c r="B5169" t="n">
+        <v>1967078</v>
+      </c>
+      <c r="C5169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5169" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5170">
+      <c r="A5170" t="n">
+        <v>5169</v>
+      </c>
+      <c r="B5170" t="n">
+        <v>1967079</v>
+      </c>
+      <c r="C5170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5170" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5171">
+      <c r="A5171" t="n">
+        <v>5170</v>
+      </c>
+      <c r="B5171" t="n">
+        <v>1967080</v>
+      </c>
+      <c r="C5171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5171" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5172">
+      <c r="A5172" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B5172" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5172" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5172" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5172" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5173">
+      <c r="A5173" t="n">
+        <v>5172</v>
+      </c>
+      <c r="B5173" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5173" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5173" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5173" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:31]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5174">
+      <c r="A5174" t="n">
+        <v>5173</v>
+      </c>
+      <c r="B5174" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5174" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5174" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5175">
+      <c r="A5175" t="n">
+        <v>5174</v>
+      </c>
+      <c r="B5175" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5175" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5176">
+      <c r="A5176" t="n">
+        <v>5175</v>
+      </c>
+      <c r="B5176" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5176" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5177">
+      <c r="A5177" t="n">
+        <v>5176</v>
+      </c>
+      <c r="B5177" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5177" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5177" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5177" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:34]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5178">
+      <c r="A5178" t="n">
+        <v>5177</v>
+      </c>
+      <c r="B5178" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+      <c r="C5178" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+      <c r="D5178" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+      <c r="E5178" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+    </row>
+    <row r="5179">
+      <c r="A5179" t="n">
+        <v>5178</v>
+      </c>
+      <c r="B5179" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5179" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5179" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5179" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:36]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5180">
+      <c r="A5180" t="n">
+        <v>5179</v>
+      </c>
+      <c r="B5180" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+      <c r="C5180" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+      <c r="D5180" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+      <c r="E5180" t="inlineStr">
+        <is>
+          <t>----------</t>
+        </is>
+      </c>
+    </row>
+    <row r="5181">
+      <c r="A5181" t="n">
+        <v>5180</v>
+      </c>
+      <c r="B5181" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5181" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5181" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5181" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5182">
+      <c r="A5182" t="n">
+        <v>5181</v>
+      </c>
+      <c r="B5182" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5182" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5182" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5183">
+      <c r="A5183" t="n">
+        <v>5182</v>
+      </c>
+      <c r="B5183" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5183" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5183" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5184">
+      <c r="A5184" t="n">
+        <v>5183</v>
+      </c>
+      <c r="B5184" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5184" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5185">
+      <c r="A5185" t="n">
+        <v>5184</v>
+      </c>
+      <c r="B5185" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5185" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5185" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5185" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:46]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5186">
+      <c r="A5186" t="n">
+        <v>5185</v>
+      </c>
+      <c r="B5186" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5186" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5186" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5187">
+      <c r="A5187" t="n">
+        <v>5186</v>
+      </c>
+      <c r="B5187" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5187" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5187" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5188">
+      <c r="A5188" t="n">
+        <v>5187</v>
+      </c>
+      <c r="B5188" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5188" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5188" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5188" t="inlineStr">
+        <is>
+          <t>[09-02-2026 16:51]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5189">
+      <c r="A5189" t="n">
+        <v>5188</v>
+      </c>
+      <c r="B5189" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5189" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5189" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5190">
+      <c r="A5190" t="n">
+        <v>5189</v>
+      </c>
+      <c r="B5190" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5190" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5191">
+      <c r="A5191" t="n">
+        <v>5190</v>
+      </c>
+      <c r="B5191" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5191" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5191" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5192">
+      <c r="A5192" t="n">
+        <v>5191</v>
+      </c>
+      <c r="B5192" t="n">
+        <v>1936999</v>
+      </c>
+      <c r="C5192" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5192" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5193">
+      <c r="A5193" t="n">
+        <v>5192</v>
+      </c>
+      <c r="B5193" t="n">
+        <v>1973112</v>
+      </c>
+      <c r="C5193" t="inlineStr">
+        <is>
+          <t>PUBLICA</t>
+        </is>
+      </c>
+      <c r="D5193" t="inlineStr">
+        <is>
+          <t>PUBLICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5194">
+      <c r="A5194" t="n">
+        <v>5193</v>
+      </c>
+      <c r="B5194" t="n">
+        <v>1974255</v>
+      </c>
+      <c r="C5194" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5194" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5195">
+      <c r="A5195" t="n">
+        <v>5194</v>
+      </c>
+      <c r="B5195" t="n">
+        <v>2022099</v>
+      </c>
+      <c r="C5195" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5195" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5196">
+      <c r="A5196" t="n">
+        <v>5195</v>
+      </c>
+      <c r="B5196" t="n">
+        <v>2022706</v>
+      </c>
+      <c r="C5196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5196" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5197">
+      <c r="A5197" t="n">
+        <v>5196</v>
+      </c>
+      <c r="B5197" t="n">
+        <v>2043241</v>
+      </c>
+      <c r="C5197" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5197" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5198">
+      <c r="A5198" t="n">
+        <v>5197</v>
+      </c>
+      <c r="B5198" t="n">
+        <v>2043242</v>
+      </c>
+      <c r="C5198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5198" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5199">
+      <c r="A5199" t="n">
+        <v>5198</v>
+      </c>
+      <c r="B5199" t="n">
+        <v>2043253</v>
+      </c>
+      <c r="C5199" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5199" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5200">
+      <c r="A5200" t="n">
+        <v>5199</v>
+      </c>
+      <c r="B5200" t="n">
+        <v>2043254</v>
+      </c>
+      <c r="C5200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5200" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5201">
+      <c r="A5201" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B5201" t="n">
+        <v>2043255</v>
+      </c>
+      <c r="C5201" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5201" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5202">
+      <c r="A5202" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B5202" t="n">
+        <v>2043256</v>
+      </c>
+      <c r="C5202" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5202" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5203">
+      <c r="A5203" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B5203" t="n">
+        <v>2043258</v>
+      </c>
+      <c r="C5203" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5203" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5204">
+      <c r="A5204" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B5204" t="n">
+        <v>2043260</v>
+      </c>
+      <c r="C5204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5204" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5205">
+      <c r="A5205" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B5205" t="n">
+        <v>2102277</v>
+      </c>
+      <c r="C5205" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5205" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5206">
+      <c r="A5206" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B5206" t="n">
+        <v>2119576</v>
+      </c>
+      <c r="C5206" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5206" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5207">
+      <c r="A5207" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B5207" t="n">
+        <v>2123870</v>
+      </c>
+      <c r="C5207" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5207" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5208">
+      <c r="A5208" t="n">
+        <v>5207</v>
+      </c>
+      <c r="B5208" t="n">
+        <v>2126325</v>
+      </c>
+      <c r="C5208" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5208" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5209">
+      <c r="A5209" t="n">
+        <v>5208</v>
+      </c>
+      <c r="B5209" t="n">
+        <v>2126326</v>
+      </c>
+      <c r="C5209" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5209" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5210">
+      <c r="A5210" t="n">
+        <v>5209</v>
+      </c>
+      <c r="B5210" t="n">
+        <v>2126327</v>
+      </c>
+      <c r="C5210" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5210" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5211">
+      <c r="A5211" t="n">
+        <v>5210</v>
+      </c>
+      <c r="B5211" t="n">
+        <v>2126328</v>
+      </c>
+      <c r="C5211" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5211" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5212">
+      <c r="A5212" t="n">
+        <v>5211</v>
+      </c>
+      <c r="B5212" t="n">
+        <v>2126329</v>
+      </c>
+      <c r="C5212" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5212" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5213">
+      <c r="A5213" t="n">
+        <v>5212</v>
+      </c>
+      <c r="B5213" t="n">
+        <v>2126330</v>
+      </c>
+      <c r="C5213" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5213" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5214">
+      <c r="A5214" t="n">
+        <v>5213</v>
+      </c>
+      <c r="B5214" t="n">
+        <v>2126331</v>
+      </c>
+      <c r="C5214" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5214" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5215">
+      <c r="A5215" t="n">
+        <v>5214</v>
+      </c>
+      <c r="B5215" t="n">
+        <v>2126332</v>
+      </c>
+      <c r="C5215" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5215" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5216">
+      <c r="A5216" t="n">
+        <v>5215</v>
+      </c>
+      <c r="B5216" t="n">
+        <v>2126333</v>
+      </c>
+      <c r="C5216" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5216" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5217">
+      <c r="A5217" t="n">
+        <v>5216</v>
+      </c>
+      <c r="B5217" t="n">
+        <v>2126334</v>
+      </c>
+      <c r="C5217" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5217" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5218">
+      <c r="A5218" t="n">
+        <v>5217</v>
+      </c>
+      <c r="B5218" t="n">
+        <v>2126335</v>
+      </c>
+      <c r="C5218" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5218" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5219">
+      <c r="A5219" t="n">
+        <v>5218</v>
+      </c>
+      <c r="B5219" t="n">
+        <v>2126336</v>
+      </c>
+      <c r="C5219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5219" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" t="n">
+        <v>5219</v>
+      </c>
+      <c r="B5220" t="n">
+        <v>2126337</v>
+      </c>
+      <c r="C5220" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5220" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5221">
+      <c r="A5221" t="n">
+        <v>5220</v>
+      </c>
+      <c r="B5221" t="n">
+        <v>2126338</v>
+      </c>
+      <c r="C5221" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5221" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" t="n">
+        <v>5221</v>
+      </c>
+      <c r="B5222" t="n">
+        <v>2126339</v>
+      </c>
+      <c r="C5222" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5222" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="n">
+        <v>5222</v>
+      </c>
+      <c r="B5223" t="n">
+        <v>2126340</v>
+      </c>
+      <c r="C5223" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5223" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" t="n">
+        <v>5223</v>
+      </c>
+      <c r="B5224" t="n">
+        <v>2126341</v>
+      </c>
+      <c r="C5224" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5224" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="n">
+        <v>5224</v>
+      </c>
+      <c r="B5225" t="n">
+        <v>2126342</v>
+      </c>
+      <c r="C5225" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5225" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" t="n">
+        <v>5225</v>
+      </c>
+      <c r="B5226" t="n">
+        <v>2126343</v>
+      </c>
+      <c r="C5226" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5226" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="n">
+        <v>5226</v>
+      </c>
+      <c r="B5227" t="n">
+        <v>2126344</v>
+      </c>
+      <c r="C5227" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5227" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" t="n">
+        <v>5227</v>
+      </c>
+      <c r="B5228" t="n">
+        <v>2126345</v>
+      </c>
+      <c r="C5228" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5228" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="n">
+        <v>5228</v>
+      </c>
+      <c r="B5229" t="n">
+        <v>2126346</v>
+      </c>
+      <c r="C5229" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5229" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" t="n">
+        <v>5229</v>
+      </c>
+      <c r="B5230" t="n">
+        <v>2126347</v>
+      </c>
+      <c r="C5230" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5230" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="n">
+        <v>5230</v>
+      </c>
+      <c r="B5231" t="n">
+        <v>2126348</v>
+      </c>
+      <c r="C5231" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5231" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" t="n">
+        <v>5231</v>
+      </c>
+      <c r="B5232" t="n">
+        <v>2126349</v>
+      </c>
+      <c r="C5232" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5232" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="n">
+        <v>5232</v>
+      </c>
+      <c r="B5233" t="n">
+        <v>2126350</v>
+      </c>
+      <c r="C5233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5233" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" t="n">
+        <v>5233</v>
+      </c>
+      <c r="B5234" t="n">
+        <v>2126351</v>
+      </c>
+      <c r="C5234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5234" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="n">
+        <v>5234</v>
+      </c>
+      <c r="B5235" t="n">
+        <v>2126352</v>
+      </c>
+      <c r="C5235" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5235" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" t="n">
+        <v>5235</v>
+      </c>
+      <c r="B5236" t="n">
+        <v>2126353</v>
+      </c>
+      <c r="C5236" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5236" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="n">
+        <v>5236</v>
+      </c>
+      <c r="B5237" t="n">
+        <v>2126354</v>
+      </c>
+      <c r="C5237" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5237" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" t="n">
+        <v>5237</v>
+      </c>
+      <c r="B5238" t="n">
+        <v>2126355</v>
+      </c>
+      <c r="C5238" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5238" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="n">
+        <v>5238</v>
+      </c>
+      <c r="B5239" t="n">
+        <v>2126356</v>
+      </c>
+      <c r="C5239" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5239" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" t="n">
+        <v>5239</v>
+      </c>
+      <c r="B5240" t="n">
+        <v>2126357</v>
+      </c>
+      <c r="C5240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5240" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="n">
+        <v>5240</v>
+      </c>
+      <c r="B5241" t="n">
+        <v>2126358</v>
+      </c>
+      <c r="C5241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5241" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" t="n">
+        <v>5241</v>
+      </c>
+      <c r="B5242" t="n">
+        <v>2126359</v>
+      </c>
+      <c r="C5242" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5242" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="n">
+        <v>5242</v>
+      </c>
+      <c r="B5243" t="n">
+        <v>2126360</v>
+      </c>
+      <c r="C5243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5243" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" t="n">
+        <v>5243</v>
+      </c>
+      <c r="B5244" t="n">
+        <v>2126361</v>
+      </c>
+      <c r="C5244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5244" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="n">
+        <v>5244</v>
+      </c>
+      <c r="B5245" t="n">
+        <v>2126362</v>
+      </c>
+      <c r="C5245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5245" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" t="n">
+        <v>5245</v>
+      </c>
+      <c r="B5246" t="n">
+        <v>2126363</v>
+      </c>
+      <c r="C5246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5246" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="n">
+        <v>5246</v>
+      </c>
+      <c r="B5247" t="n">
+        <v>2126364</v>
+      </c>
+      <c r="C5247" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5247" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" t="n">
+        <v>5247</v>
+      </c>
+      <c r="B5248" t="n">
+        <v>2126365</v>
+      </c>
+      <c r="C5248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5248" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="n">
+        <v>5248</v>
+      </c>
+      <c r="B5249" t="n">
+        <v>2126366</v>
+      </c>
+      <c r="C5249" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5249" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" t="n">
+        <v>5249</v>
+      </c>
+      <c r="B5250" t="n">
+        <v>2126367</v>
+      </c>
+      <c r="C5250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5250" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="n">
+        <v>5250</v>
+      </c>
+      <c r="B5251" t="n">
+        <v>2126368</v>
+      </c>
+      <c r="C5251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5251" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" t="n">
+        <v>5251</v>
+      </c>
+      <c r="B5252" t="n">
+        <v>2126369</v>
+      </c>
+      <c r="C5252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5252" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="n">
+        <v>5252</v>
+      </c>
+      <c r="B5253" t="n">
+        <v>2128087</v>
+      </c>
+      <c r="C5253" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+      <c r="D5253" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" t="n">
+        <v>5253</v>
+      </c>
+      <c r="B5254" t="n">
+        <v>2131999</v>
+      </c>
+      <c r="C5254" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+      <c r="D5254" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="n">
+        <v>5254</v>
+      </c>
+      <c r="B5255" t="n">
+        <v>2132000</v>
+      </c>
+      <c r="C5255" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5255" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" t="n">
+        <v>5255</v>
+      </c>
+      <c r="B5256" t="n">
+        <v>2132001</v>
+      </c>
+      <c r="C5256" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+      <c r="D5256" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="n">
+        <v>5256</v>
+      </c>
+      <c r="B5257" t="n">
+        <v>2132002</v>
+      </c>
+      <c r="C5257" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5257" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" t="n">
+        <v>5257</v>
+      </c>
+      <c r="B5258" t="n">
+        <v>2132003</v>
+      </c>
+      <c r="C5258" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5258" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="n">
+        <v>5258</v>
+      </c>
+      <c r="B5259" t="n">
+        <v>2132004</v>
+      </c>
+      <c r="C5259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5259" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" t="n">
+        <v>5259</v>
+      </c>
+      <c r="B5260" t="n">
+        <v>2155155</v>
+      </c>
+      <c r="C5260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5260" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="n">
+        <v>5260</v>
+      </c>
+      <c r="B5261" t="n">
+        <v>2155944</v>
+      </c>
+      <c r="C5261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5261" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" t="n">
+        <v>5261</v>
+      </c>
+      <c r="B5262" t="n">
+        <v>2167003</v>
+      </c>
+      <c r="C5262" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5262" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="n">
+        <v>5262</v>
+      </c>
+      <c r="B5263" t="n">
+        <v>2180667</v>
+      </c>
+      <c r="C5263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5263" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" t="n">
+        <v>5263</v>
+      </c>
+      <c r="B5264" t="n">
+        <v>2190733</v>
+      </c>
+      <c r="C5264" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+      <c r="D5264" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="n">
+        <v>5264</v>
+      </c>
+      <c r="B5265" t="n">
+        <v>2197165</v>
+      </c>
+      <c r="C5265" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5265" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" t="n">
+        <v>5265</v>
+      </c>
+      <c r="B5266" t="n">
+        <v>2197172</v>
+      </c>
+      <c r="C5266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5266" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="n">
+        <v>5266</v>
+      </c>
+      <c r="B5267" t="n">
+        <v>2198570</v>
+      </c>
+      <c r="C5267" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5267" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" t="n">
+        <v>5267</v>
+      </c>
+      <c r="B5268" t="n">
+        <v>2199941</v>
+      </c>
+      <c r="C5268" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5268" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="n">
+        <v>5268</v>
+      </c>
+      <c r="B5269" t="n">
+        <v>2199962</v>
+      </c>
+      <c r="C5269" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5269" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" t="n">
+        <v>5269</v>
+      </c>
+      <c r="B5270" t="n">
+        <v>2199964</v>
+      </c>
+      <c r="C5270" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5270" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="n">
+        <v>5270</v>
+      </c>
+      <c r="B5271" t="n">
+        <v>2202748</v>
+      </c>
+      <c r="C5271" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5271" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" t="n">
+        <v>5271</v>
+      </c>
+      <c r="B5272" t="n">
+        <v>2204670</v>
+      </c>
+      <c r="C5272" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5272" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="n">
+        <v>5272</v>
+      </c>
+      <c r="B5273" t="n">
+        <v>2204781</v>
+      </c>
+      <c r="C5273" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+      <c r="D5273" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" t="n">
+        <v>5273</v>
+      </c>
+      <c r="B5274" t="n">
+        <v>2204783</v>
+      </c>
+      <c r="C5274" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+      <c r="D5274" t="inlineStr">
+        <is>
+          <t>YA PUBLICADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="n">
+        <v>5274</v>
+      </c>
+      <c r="B5275" t="n">
+        <v>2212113</v>
+      </c>
+      <c r="C5275" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5275" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" t="n">
+        <v>5275</v>
+      </c>
+      <c r="B5276" t="n">
+        <v>2212272</v>
+      </c>
+      <c r="C5276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5276" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="n">
+        <v>5276</v>
+      </c>
+      <c r="B5277" t="n">
+        <v>2212442</v>
+      </c>
+      <c r="C5277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5277" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" t="n">
+        <v>5277</v>
+      </c>
+      <c r="B5278" t="n">
+        <v>2212443</v>
+      </c>
+      <c r="C5278" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5278" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="n">
+        <v>5278</v>
+      </c>
+      <c r="B5279" t="n">
+        <v>2212467</v>
+      </c>
+      <c r="C5279" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5279" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" t="n">
+        <v>5279</v>
+      </c>
+      <c r="B5280" t="n">
+        <v>2212473</v>
+      </c>
+      <c r="C5280" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5280" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="n">
+        <v>5280</v>
+      </c>
+      <c r="B5281" t="n">
+        <v>2215908</v>
+      </c>
+      <c r="C5281" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5281" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" t="n">
+        <v>5281</v>
+      </c>
+      <c r="B5282" t="n">
+        <v>2215953</v>
+      </c>
+      <c r="C5282" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5282" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="n">
+        <v>5282</v>
+      </c>
+      <c r="B5283" t="n">
+        <v>2216085</v>
+      </c>
+      <c r="C5283" t="inlineStr">
+        <is>
+          <t>PUBLICA</t>
+        </is>
+      </c>
+      <c r="D5283" t="inlineStr">
+        <is>
+          <t>PUBLICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" t="n">
+        <v>5283</v>
+      </c>
+      <c r="B5284" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5284" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5284" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5284" t="inlineStr">
+        <is>
+          <t>[09-02-2026 17:28]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="n">
+        <v>5284</v>
+      </c>
+      <c r="B5285" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5285" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5285" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" t="n">
+        <v>5285</v>
+      </c>
+      <c r="B5286" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5286" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5286" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="n">
+        <v>5286</v>
+      </c>
+      <c r="B5287" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5287" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5287" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5288">
+      <c r="A5288" t="n">
+        <v>5287</v>
+      </c>
+      <c r="B5288" t="n">
+        <v>1936999</v>
+      </c>
+      <c r="C5288" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5288" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="n">
+        <v>5288</v>
+      </c>
+      <c r="B5289" t="n">
+        <v>1974255</v>
+      </c>
+      <c r="C5289" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5289" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" t="n">
+        <v>5289</v>
+      </c>
+      <c r="B5290" t="n">
+        <v>2022099</v>
+      </c>
+      <c r="C5290" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5290" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="n">
+        <v>5290</v>
+      </c>
+      <c r="B5291" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5291" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5291" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5291" t="inlineStr">
+        <is>
+          <t>[09-02-2026 17:33]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" t="n">
+        <v>5291</v>
+      </c>
+      <c r="B5292" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5292" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5292" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="n">
+        <v>5292</v>
+      </c>
+      <c r="B5293" t="n">
+        <v>1806771</v>
+      </c>
+      <c r="C5293" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5293" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" t="n">
+        <v>5293</v>
+      </c>
+      <c r="B5294" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5294" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="n">
+        <v>5294</v>
+      </c>
+      <c r="B5295" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5295" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5295" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" t="n">
+        <v>5295</v>
+      </c>
+      <c r="B5296" t="n">
+        <v>1936999</v>
+      </c>
+      <c r="C5296" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5296" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="n">
+        <v>5296</v>
+      </c>
+      <c r="B5297" t="n">
+        <v>1974255</v>
+      </c>
+      <c r="C5297" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5297" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" t="n">
+        <v>5297</v>
+      </c>
+      <c r="B5298" t="n">
+        <v>2020984</v>
+      </c>
+      <c r="C5298" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5298" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="n">
+        <v>5298</v>
+      </c>
+      <c r="B5299" t="n">
+        <v>2022099</v>
+      </c>
+      <c r="C5299" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5299" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" t="n">
+        <v>5299</v>
+      </c>
+      <c r="B5300" t="n">
+        <v>2022706</v>
+      </c>
+      <c r="C5300" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5300" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="n">
+        <v>5300</v>
+      </c>
+      <c r="B5301" t="n">
+        <v>2043242</v>
+      </c>
+      <c r="C5301" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5301" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" t="n">
+        <v>5301</v>
+      </c>
+      <c r="B5302" t="n">
+        <v>2043255</v>
+      </c>
+      <c r="C5302" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5302" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="n">
+        <v>5302</v>
+      </c>
+      <c r="B5303" t="n">
+        <v>2043256</v>
+      </c>
+      <c r="C5303" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5303" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" t="n">
+        <v>5303</v>
+      </c>
+      <c r="B5304" t="n">
+        <v>2043258</v>
+      </c>
+      <c r="C5304" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5304" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="n">
+        <v>5304</v>
+      </c>
+      <c r="B5305" t="n">
+        <v>2043260</v>
+      </c>
+      <c r="C5305" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5305" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" t="n">
+        <v>5305</v>
+      </c>
+      <c r="B5306" t="n">
+        <v>2080977</v>
+      </c>
+      <c r="C5306" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5306" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5307">
+      <c r="A5307" t="n">
+        <v>5306</v>
+      </c>
+      <c r="B5307" t="n">
+        <v>2082345</v>
+      </c>
+      <c r="C5307" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5307" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" t="n">
+        <v>5307</v>
+      </c>
+      <c r="B5308" t="n">
+        <v>2102277</v>
+      </c>
+      <c r="C5308" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5308" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="n">
+        <v>5308</v>
+      </c>
+      <c r="B5309" t="n">
+        <v>2119576</v>
+      </c>
+      <c r="C5309" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5309" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" t="n">
+        <v>5309</v>
+      </c>
+      <c r="B5310" t="n">
+        <v>2123870</v>
+      </c>
+      <c r="C5310" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5310" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B5311" t="n">
+        <v>2126325</v>
+      </c>
+      <c r="C5311" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5311" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" t="n">
+        <v>5311</v>
+      </c>
+      <c r="B5312" t="n">
+        <v>2126326</v>
+      </c>
+      <c r="C5312" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5312" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B5313" t="n">
+        <v>2126327</v>
+      </c>
+      <c r="C5313" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B5314" t="n">
+        <v>2126328</v>
+      </c>
+      <c r="C5314" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5314" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B5315" t="n">
+        <v>2126329</v>
+      </c>
+      <c r="C5315" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5315" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" t="n">
+        <v>5315</v>
+      </c>
+      <c r="B5316" t="n">
+        <v>2126330</v>
+      </c>
+      <c r="C5316" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5316" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="n">
+        <v>5316</v>
+      </c>
+      <c r="B5317" t="n">
+        <v>2126331</v>
+      </c>
+      <c r="C5317" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5317" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" t="n">
+        <v>5317</v>
+      </c>
+      <c r="B5318" t="n">
+        <v>2126332</v>
+      </c>
+      <c r="C5318" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5318" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="n">
+        <v>5318</v>
+      </c>
+      <c r="B5319" t="n">
+        <v>2126333</v>
+      </c>
+      <c r="C5319" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5319" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5320">
+      <c r="A5320" t="n">
+        <v>5319</v>
+      </c>
+      <c r="B5320" t="n">
+        <v>2126334</v>
+      </c>
+      <c r="C5320" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5320" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5321">
+      <c r="A5321" t="n">
+        <v>5320</v>
+      </c>
+      <c r="B5321" t="n">
+        <v>2126335</v>
+      </c>
+      <c r="C5321" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5321" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5322">
+      <c r="A5322" t="n">
+        <v>5321</v>
+      </c>
+      <c r="B5322" t="n">
+        <v>2126336</v>
+      </c>
+      <c r="C5322" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5322" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5323">
+      <c r="A5323" t="n">
+        <v>5322</v>
+      </c>
+      <c r="B5323" t="n">
+        <v>2126337</v>
+      </c>
+      <c r="C5323" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5323" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5324">
+      <c r="A5324" t="n">
+        <v>5323</v>
+      </c>
+      <c r="B5324" t="n">
+        <v>2126338</v>
+      </c>
+      <c r="C5324" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5324" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5325">
+      <c r="A5325" t="n">
+        <v>5324</v>
+      </c>
+      <c r="B5325" t="n">
+        <v>2126339</v>
+      </c>
+      <c r="C5325" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5325" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5326">
+      <c r="A5326" t="n">
+        <v>5325</v>
+      </c>
+      <c r="B5326" t="n">
+        <v>2126340</v>
+      </c>
+      <c r="C5326" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5326" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5327">
+      <c r="A5327" t="n">
+        <v>5326</v>
+      </c>
+      <c r="B5327" t="n">
+        <v>2126341</v>
+      </c>
+      <c r="C5327" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5327" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5328">
+      <c r="A5328" t="n">
+        <v>5327</v>
+      </c>
+      <c r="B5328" t="n">
+        <v>2126342</v>
+      </c>
+      <c r="C5328" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5328" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5329">
+      <c r="A5329" t="n">
+        <v>5328</v>
+      </c>
+      <c r="B5329" t="n">
+        <v>2126343</v>
+      </c>
+      <c r="C5329" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5329" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5330">
+      <c r="A5330" t="n">
+        <v>5329</v>
+      </c>
+      <c r="B5330" t="n">
+        <v>2126344</v>
+      </c>
+      <c r="C5330" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5330" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5331">
+      <c r="A5331" t="n">
+        <v>5330</v>
+      </c>
+      <c r="B5331" t="n">
+        <v>2126345</v>
+      </c>
+      <c r="C5331" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5331" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5332">
+      <c r="A5332" t="n">
+        <v>5331</v>
+      </c>
+      <c r="B5332" t="n">
+        <v>2126346</v>
+      </c>
+      <c r="C5332" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5332" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5333">
+      <c r="A5333" t="n">
+        <v>5332</v>
+      </c>
+      <c r="B5333" t="n">
+        <v>2126347</v>
+      </c>
+      <c r="C5333" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5333" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5334">
+      <c r="A5334" t="n">
+        <v>5333</v>
+      </c>
+      <c r="B5334" t="n">
+        <v>2126348</v>
+      </c>
+      <c r="C5334" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5334" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5335">
+      <c r="A5335" t="n">
+        <v>5334</v>
+      </c>
+      <c r="B5335" t="n">
+        <v>2126349</v>
+      </c>
+      <c r="C5335" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5335" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5336">
+      <c r="A5336" t="n">
+        <v>5335</v>
+      </c>
+      <c r="B5336" t="n">
+        <v>2126350</v>
+      </c>
+      <c r="C5336" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5336" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5337">
+      <c r="A5337" t="n">
+        <v>5336</v>
+      </c>
+      <c r="B5337" t="n">
+        <v>2126351</v>
+      </c>
+      <c r="C5337" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5337" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5338">
+      <c r="A5338" t="n">
+        <v>5337</v>
+      </c>
+      <c r="B5338" t="n">
+        <v>2126352</v>
+      </c>
+      <c r="C5338" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5338" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5339">
+      <c r="A5339" t="n">
+        <v>5338</v>
+      </c>
+      <c r="B5339" t="n">
+        <v>2126353</v>
+      </c>
+      <c r="C5339" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5339" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5340">
+      <c r="A5340" t="n">
+        <v>5339</v>
+      </c>
+      <c r="B5340" t="n">
+        <v>2126354</v>
+      </c>
+      <c r="C5340" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5340" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5341">
+      <c r="A5341" t="n">
+        <v>5340</v>
+      </c>
+      <c r="B5341" t="n">
+        <v>2126355</v>
+      </c>
+      <c r="C5341" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5341" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5342">
+      <c r="A5342" t="n">
+        <v>5341</v>
+      </c>
+      <c r="B5342" t="n">
+        <v>2126356</v>
+      </c>
+      <c r="C5342" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5342" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5343">
+      <c r="A5343" t="n">
+        <v>5342</v>
+      </c>
+      <c r="B5343" t="n">
+        <v>2126357</v>
+      </c>
+      <c r="C5343" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5343" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5344">
+      <c r="A5344" t="n">
+        <v>5343</v>
+      </c>
+      <c r="B5344" t="n">
+        <v>2126358</v>
+      </c>
+      <c r="C5344" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5344" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5345">
+      <c r="A5345" t="n">
+        <v>5344</v>
+      </c>
+      <c r="B5345" t="n">
+        <v>2126359</v>
+      </c>
+      <c r="C5345" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5345" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5346">
+      <c r="A5346" t="n">
+        <v>5345</v>
+      </c>
+      <c r="B5346" t="n">
+        <v>2126360</v>
+      </c>
+      <c r="C5346" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5346" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5347">
+      <c r="A5347" t="n">
+        <v>5346</v>
+      </c>
+      <c r="B5347" t="n">
+        <v>2126361</v>
+      </c>
+      <c r="C5347" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5347" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5348">
+      <c r="A5348" t="n">
+        <v>5347</v>
+      </c>
+      <c r="B5348" t="n">
+        <v>2126362</v>
+      </c>
+      <c r="C5348" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5348" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5349">
+      <c r="A5349" t="n">
+        <v>5348</v>
+      </c>
+      <c r="B5349" t="n">
+        <v>2126363</v>
+      </c>
+      <c r="C5349" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5349" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5350">
+      <c r="A5350" t="n">
+        <v>5349</v>
+      </c>
+      <c r="B5350" t="n">
+        <v>2126364</v>
+      </c>
+      <c r="C5350" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5350" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5351">
+      <c r="A5351" t="n">
+        <v>5350</v>
+      </c>
+      <c r="B5351" t="n">
+        <v>2126365</v>
+      </c>
+      <c r="C5351" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5351" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5352">
+      <c r="A5352" t="n">
+        <v>5351</v>
+      </c>
+      <c r="B5352" t="n">
+        <v>2126366</v>
+      </c>
+      <c r="C5352" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5352" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5353">
+      <c r="A5353" t="n">
+        <v>5352</v>
+      </c>
+      <c r="B5353" t="n">
+        <v>2126367</v>
+      </c>
+      <c r="C5353" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5353" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5354">
+      <c r="A5354" t="n">
+        <v>5353</v>
+      </c>
+      <c r="B5354" t="n">
+        <v>2126368</v>
+      </c>
+      <c r="C5354" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5354" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="n">
+        <v>5354</v>
+      </c>
+      <c r="B5355" t="n">
+        <v>2126369</v>
+      </c>
+      <c r="C5355" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5355" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" t="n">
+        <v>5355</v>
+      </c>
+      <c r="B5356" t="n">
+        <v>2132000</v>
+      </c>
+      <c r="C5356" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5356" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="n">
+        <v>5356</v>
+      </c>
+      <c r="B5357" t="n">
+        <v>2132002</v>
+      </c>
+      <c r="C5357" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5357" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" t="n">
+        <v>5357</v>
+      </c>
+      <c r="B5358" t="n">
+        <v>2132003</v>
+      </c>
+      <c r="C5358" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5358" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="n">
+        <v>5358</v>
+      </c>
+      <c r="B5359" t="n">
+        <v>2132004</v>
+      </c>
+      <c r="C5359" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5359" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" t="n">
+        <v>5359</v>
+      </c>
+      <c r="B5360" t="n">
+        <v>2139788</v>
+      </c>
+      <c r="C5360" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5360" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="n">
+        <v>5360</v>
+      </c>
+      <c r="B5361" t="n">
+        <v>2139795</v>
+      </c>
+      <c r="C5361" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5361" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" t="n">
+        <v>5361</v>
+      </c>
+      <c r="B5362" t="n">
+        <v>2155155</v>
+      </c>
+      <c r="C5362" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5362" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="n">
+        <v>5362</v>
+      </c>
+      <c r="B5363" t="n">
+        <v>2155944</v>
+      </c>
+      <c r="C5363" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5363" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" t="n">
+        <v>5363</v>
+      </c>
+      <c r="B5364" t="n">
+        <v>2167003</v>
+      </c>
+      <c r="C5364" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5364" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="n">
+        <v>5364</v>
+      </c>
+      <c r="B5365" t="n">
+        <v>2180667</v>
+      </c>
+      <c r="C5365" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5365" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5366">
+      <c r="A5366" t="n">
+        <v>5365</v>
+      </c>
+      <c r="B5366" t="n">
+        <v>2197165</v>
+      </c>
+      <c r="C5366" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5366" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5367">
+      <c r="A5367" t="n">
+        <v>5366</v>
+      </c>
+      <c r="B5367" t="n">
+        <v>2197172</v>
+      </c>
+      <c r="C5367" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5367" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5368">
+      <c r="A5368" t="n">
+        <v>5367</v>
+      </c>
+      <c r="B5368" t="n">
+        <v>2198570</v>
+      </c>
+      <c r="C5368" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5368" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5369">
+      <c r="A5369" t="n">
+        <v>5368</v>
+      </c>
+      <c r="B5369" t="n">
+        <v>2199941</v>
+      </c>
+      <c r="C5369" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5369" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5370">
+      <c r="A5370" t="n">
+        <v>5369</v>
+      </c>
+      <c r="B5370" t="n">
+        <v>2199962</v>
+      </c>
+      <c r="C5370" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5370" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5371">
+      <c r="A5371" t="n">
+        <v>5370</v>
+      </c>
+      <c r="B5371" t="n">
+        <v>2199964</v>
+      </c>
+      <c r="C5371" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5371" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5372">
+      <c r="A5372" t="n">
+        <v>5371</v>
+      </c>
+      <c r="B5372" t="n">
+        <v>2202748</v>
+      </c>
+      <c r="C5372" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5372" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5373">
+      <c r="A5373" t="n">
+        <v>5372</v>
+      </c>
+      <c r="B5373" t="n">
+        <v>2204668</v>
+      </c>
+      <c r="C5373" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5373" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5374">
+      <c r="A5374" t="n">
+        <v>5373</v>
+      </c>
+      <c r="B5374" t="n">
+        <v>2204670</v>
+      </c>
+      <c r="C5374" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5374" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5375">
+      <c r="A5375" t="n">
+        <v>5374</v>
+      </c>
+      <c r="B5375" t="n">
+        <v>2212113</v>
+      </c>
+      <c r="C5375" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5375" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5376">
+      <c r="A5376" t="n">
+        <v>5375</v>
+      </c>
+      <c r="B5376" t="n">
+        <v>2212272</v>
+      </c>
+      <c r="C5376" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5376" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5377">
+      <c r="A5377" t="n">
+        <v>5376</v>
+      </c>
+      <c r="B5377" t="n">
+        <v>2212442</v>
+      </c>
+      <c r="C5377" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5377" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5378">
+      <c r="A5378" t="n">
+        <v>5377</v>
+      </c>
+      <c r="B5378" t="n">
+        <v>2212443</v>
+      </c>
+      <c r="C5378" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5378" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5379">
+      <c r="A5379" t="n">
+        <v>5378</v>
+      </c>
+      <c r="B5379" t="n">
+        <v>2212467</v>
+      </c>
+      <c r="C5379" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5379" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5380">
+      <c r="A5380" t="n">
+        <v>5379</v>
+      </c>
+      <c r="B5380" t="n">
+        <v>2212473</v>
+      </c>
+      <c r="C5380" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5380" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5381">
+      <c r="A5381" t="n">
+        <v>5380</v>
+      </c>
+      <c r="B5381" t="n">
+        <v>2215792</v>
+      </c>
+      <c r="C5381" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5381" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5382">
+      <c r="A5382" t="n">
+        <v>5381</v>
+      </c>
+      <c r="B5382" t="n">
+        <v>2215908</v>
+      </c>
+      <c r="C5382" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5382" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5383">
+      <c r="A5383" t="n">
+        <v>5382</v>
+      </c>
+      <c r="B5383" t="n">
+        <v>2215953</v>
+      </c>
+      <c r="C5383" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5383" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5384">
+      <c r="A5384" t="n">
+        <v>5383</v>
+      </c>
+      <c r="B5384" t="n">
+        <v>2216204</v>
+      </c>
+      <c r="C5384" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5384" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5385">
+      <c r="A5385" t="n">
+        <v>5384</v>
+      </c>
+      <c r="B5385" t="n">
+        <v>2216334</v>
+      </c>
+      <c r="C5385" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5385" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5386">
+      <c r="A5386" t="n">
+        <v>5385</v>
+      </c>
+      <c r="B5386" t="n">
+        <v>2216386</v>
+      </c>
+      <c r="C5386" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5386" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5387">
+      <c r="A5387" t="n">
+        <v>5386</v>
+      </c>
+      <c r="B5387" t="n">
+        <v>2217499</v>
+      </c>
+      <c r="C5387" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5387" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5388">
+      <c r="A5388" t="n">
+        <v>5387</v>
+      </c>
+      <c r="B5388" t="n">
+        <v>2217500</v>
+      </c>
+      <c r="C5388" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5388" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5389">
+      <c r="A5389" t="n">
+        <v>5388</v>
+      </c>
+      <c r="B5389" t="n">
+        <v>2217501</v>
+      </c>
+      <c r="C5389" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5389" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5390">
+      <c r="A5390" t="n">
+        <v>5389</v>
+      </c>
+      <c r="B5390" t="n">
+        <v>2217502</v>
+      </c>
+      <c r="C5390" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5390" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5391">
+      <c r="A5391" t="n">
+        <v>5390</v>
+      </c>
+      <c r="B5391" t="n">
+        <v>2217503</v>
+      </c>
+      <c r="C5391" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5391" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5392">
+      <c r="A5392" t="n">
+        <v>5391</v>
+      </c>
+      <c r="B5392" t="n">
+        <v>2219934</v>
+      </c>
+      <c r="C5392" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5392" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5393">
+      <c r="A5393" t="n">
+        <v>5392</v>
+      </c>
+      <c r="B5393" t="n">
+        <v>2221239</v>
+      </c>
+      <c r="C5393" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5393" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5394">
+      <c r="A5394" t="n">
+        <v>5393</v>
+      </c>
+      <c r="B5394" t="n">
+        <v>2221243</v>
+      </c>
+      <c r="C5394" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5394" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5395">
+      <c r="A5395" t="n">
+        <v>5394</v>
+      </c>
+      <c r="B5395" t="n">
+        <v>2221244</v>
+      </c>
+      <c r="C5395" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5395" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5396">
+      <c r="A5396" t="n">
+        <v>5395</v>
+      </c>
+      <c r="B5396" t="n">
+        <v>2221249</v>
+      </c>
+      <c r="C5396" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5396" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5397">
+      <c r="A5397" t="n">
+        <v>5396</v>
+      </c>
+      <c r="B5397" t="n">
+        <v>2221251</v>
+      </c>
+      <c r="C5397" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5397" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5398">
+      <c r="A5398" t="n">
+        <v>5397</v>
+      </c>
+      <c r="B5398" t="n">
+        <v>2221257</v>
+      </c>
+      <c r="C5398" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5398" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5399">
+      <c r="A5399" t="n">
+        <v>5398</v>
+      </c>
+      <c r="B5399" t="n">
+        <v>2221259</v>
+      </c>
+      <c r="C5399" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5399" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5400">
+      <c r="A5400" t="n">
+        <v>5399</v>
+      </c>
+      <c r="B5400" t="n">
+        <v>2221318</v>
+      </c>
+      <c r="C5400" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5400" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5401">
+      <c r="A5401" t="n">
+        <v>5400</v>
+      </c>
+      <c r="B5401" t="n">
+        <v>2221319</v>
+      </c>
+      <c r="C5401" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5401" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5402">
+      <c r="A5402" t="n">
+        <v>5401</v>
+      </c>
+      <c r="B5402" t="n">
+        <v>2221320</v>
+      </c>
+      <c r="C5402" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5402" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5403">
+      <c r="A5403" t="n">
+        <v>5402</v>
+      </c>
+      <c r="B5403" t="n">
+        <v>2221321</v>
+      </c>
+      <c r="C5403" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5403" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5404">
+      <c r="A5404" t="n">
+        <v>5403</v>
+      </c>
+      <c r="B5404" t="n">
+        <v>2221323</v>
+      </c>
+      <c r="C5404" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5404" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5405">
+      <c r="A5405" t="n">
+        <v>5404</v>
+      </c>
+      <c r="B5405" t="n">
+        <v>2227549</v>
+      </c>
+      <c r="C5405" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5405" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5406">
+      <c r="A5406" t="n">
+        <v>5405</v>
+      </c>
+      <c r="B5406" t="n">
+        <v>2243812</v>
+      </c>
+      <c r="C5406" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5406" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5407">
+      <c r="A5407" t="n">
+        <v>5406</v>
+      </c>
+      <c r="B5407" t="n">
+        <v>2252607</v>
+      </c>
+      <c r="C5407" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5407" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5408">
+      <c r="A5408" t="n">
+        <v>5407</v>
+      </c>
+      <c r="B5408" t="n">
+        <v>2252610</v>
+      </c>
+      <c r="C5408" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5408" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5409">
+      <c r="A5409" t="n">
+        <v>5408</v>
+      </c>
+      <c r="B5409" t="n">
+        <v>2253561</v>
+      </c>
+      <c r="C5409" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5409" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5410">
+      <c r="A5410" t="n">
+        <v>5409</v>
+      </c>
+      <c r="B5410" t="n">
+        <v>2257023</v>
+      </c>
+      <c r="C5410" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5410" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5411">
+      <c r="A5411" t="n">
+        <v>5410</v>
+      </c>
+      <c r="B5411" t="n">
+        <v>2257028</v>
+      </c>
+      <c r="C5411" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5411" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5412">
+      <c r="A5412" t="n">
+        <v>5411</v>
+      </c>
+      <c r="B5412" t="n">
+        <v>2257037</v>
+      </c>
+      <c r="C5412" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5412" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5413">
+      <c r="A5413" t="n">
+        <v>5412</v>
+      </c>
+      <c r="B5413" t="n">
+        <v>2257038</v>
+      </c>
+      <c r="C5413" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5413" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5414">
+      <c r="A5414" t="n">
+        <v>5413</v>
+      </c>
+      <c r="B5414" t="n">
+        <v>2257039</v>
+      </c>
+      <c r="C5414" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5414" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5415">
+      <c r="A5415" t="n">
+        <v>5414</v>
+      </c>
+      <c r="B5415" t="n">
+        <v>2257040</v>
+      </c>
+      <c r="C5415" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5415" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5416">
+      <c r="A5416" t="n">
+        <v>5415</v>
+      </c>
+      <c r="B5416" t="n">
+        <v>2260074</v>
+      </c>
+      <c r="C5416" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5416" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5417">
+      <c r="A5417" t="n">
+        <v>5416</v>
+      </c>
+      <c r="B5417" t="n">
+        <v>2261267</v>
+      </c>
+      <c r="C5417" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5417" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5418">
+      <c r="A5418" t="n">
+        <v>5417</v>
+      </c>
+      <c r="B5418" t="n">
+        <v>2261560</v>
+      </c>
+      <c r="C5418" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5418" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5419">
+      <c r="A5419" t="n">
+        <v>5418</v>
+      </c>
+      <c r="B5419" t="n">
+        <v>2261568</v>
+      </c>
+      <c r="C5419" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5419" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5420">
+      <c r="A5420" t="n">
+        <v>5419</v>
+      </c>
+      <c r="B5420" t="n">
+        <v>2261637</v>
+      </c>
+      <c r="C5420" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5420" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="n">
+        <v>5420</v>
+      </c>
+      <c r="B5421" t="n">
+        <v>2261642</v>
+      </c>
+      <c r="C5421" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5421" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5422">
+      <c r="A5422" t="n">
+        <v>5421</v>
+      </c>
+      <c r="B5422" t="n">
+        <v>2261664</v>
+      </c>
+      <c r="C5422" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5422" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5423">
+      <c r="A5423" t="n">
+        <v>5422</v>
+      </c>
+      <c r="B5423" t="n">
+        <v>2261674</v>
+      </c>
+      <c r="C5423" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5423" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5424">
+      <c r="A5424" t="n">
+        <v>5423</v>
+      </c>
+      <c r="B5424" t="n">
+        <v>2261777</v>
+      </c>
+      <c r="C5424" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5424" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5425">
+      <c r="A5425" t="n">
+        <v>5424</v>
+      </c>
+      <c r="B5425" t="n">
+        <v>2261919</v>
+      </c>
+      <c r="C5425" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5425" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5426">
+      <c r="A5426" t="n">
+        <v>5425</v>
+      </c>
+      <c r="B5426" t="n">
+        <v>2262330</v>
+      </c>
+      <c r="C5426" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5426" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5427">
+      <c r="A5427" t="n">
+        <v>5426</v>
+      </c>
+      <c r="B5427" t="n">
+        <v>2262677</v>
+      </c>
+      <c r="C5427" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5427" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5428">
+      <c r="A5428" t="n">
+        <v>5427</v>
+      </c>
+      <c r="B5428" t="n">
+        <v>2262813</v>
+      </c>
+      <c r="C5428" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5428" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5429">
+      <c r="A5429" t="n">
+        <v>5428</v>
+      </c>
+      <c r="B5429" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5429" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5429" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5429" t="inlineStr">
+        <is>
+          <t>[09-02-2026 18:09]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5430">
+      <c r="A5430" t="n">
+        <v>5429</v>
+      </c>
+      <c r="B5430" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5430" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5430" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5431">
+      <c r="A5431" t="n">
+        <v>5430</v>
+      </c>
+      <c r="B5431" t="n">
+        <v>1806771</v>
+      </c>
+      <c r="C5431" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5431" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5432">
+      <c r="A5432" t="n">
+        <v>5431</v>
+      </c>
+      <c r="B5432" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5432" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5432" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5432" t="inlineStr">
+        <is>
+          <t>[09-02-2026 18:15]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5433">
+      <c r="A5433" t="n">
+        <v>5432</v>
+      </c>
+      <c r="B5433" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5433" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5433" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5434">
+      <c r="A5434" t="n">
+        <v>5433</v>
+      </c>
+      <c r="B5434" t="n">
+        <v>1806771</v>
+      </c>
+      <c r="C5434" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5434" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5435">
+      <c r="A5435" t="n">
+        <v>5434</v>
+      </c>
+      <c r="B5435" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5435" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5435" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5436">
+      <c r="A5436" t="n">
+        <v>5435</v>
+      </c>
+      <c r="B5436" t="n">
+        <v>1934530</v>
+      </c>
+      <c r="C5436" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5436" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5437">
+      <c r="A5437" t="n">
+        <v>5436</v>
+      </c>
+      <c r="B5437" t="n">
+        <v>1936999</v>
+      </c>
+      <c r="C5437" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5437" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5438">
+      <c r="A5438" t="n">
+        <v>5437</v>
+      </c>
+      <c r="B5438" t="n">
+        <v>1974255</v>
+      </c>
+      <c r="C5438" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5438" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5439">
+      <c r="A5439" t="n">
+        <v>5438</v>
+      </c>
+      <c r="B5439" t="n">
+        <v>2020984</v>
+      </c>
+      <c r="C5439" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5439" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5440">
+      <c r="A5440" t="n">
+        <v>5439</v>
+      </c>
+      <c r="B5440" t="n">
+        <v>2022099</v>
+      </c>
+      <c r="C5440" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5440" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5441">
+      <c r="A5441" t="n">
+        <v>5440</v>
+      </c>
+      <c r="B5441" t="n">
+        <v>2022706</v>
+      </c>
+      <c r="C5441" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5441" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5442">
+      <c r="A5442" t="n">
+        <v>5441</v>
+      </c>
+      <c r="B5442" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="C5442" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="D5442" t="inlineStr">
+        <is>
+          <t>##########</t>
+        </is>
+      </c>
+      <c r="E5442" t="inlineStr">
+        <is>
+          <t>[09-02-2026 18:19]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5443">
+      <c r="A5443" t="n">
+        <v>5442</v>
+      </c>
+      <c r="B5443" t="n">
+        <v>1389786</v>
+      </c>
+      <c r="C5443" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5443" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5444">
+      <c r="A5444" t="n">
+        <v>5443</v>
+      </c>
+      <c r="B5444" t="n">
+        <v>1806771</v>
+      </c>
+      <c r="C5444" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+      <c r="D5444" t="inlineStr">
+        <is>
+          <t>PUBLICABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5445">
+      <c r="A5445" t="n">
+        <v>5444</v>
+      </c>
+      <c r="B5445" t="n">
+        <v>1863059</v>
+      </c>
+      <c r="C5445" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5445" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5149"/>
+  <autoFilter ref="A1:E5445"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>